--- a/Sensitivity_SSIM_Couple.xlsx
+++ b/Sensitivity_SSIM_Couple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22950E69-C714-4407-A628-9B992F08958C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CAE4A67-9C72-4E37-9D03-80DDE8285D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA562960-8E42-406F-ACC4-733D6769151A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00D9F287-3D81-4AF3-B48C-1F9774ABDEA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66DE68C9-B343-4E98-BF46-A2F6D75CE84B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4778E337-F33C-484A-9BBA-92B7300F0627}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF41C973-8A6F-4338-A501-438B64669AB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C1A52BB-91EA-4380-A825-8C591FAED4D3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE79A6C-C74C-4E8D-881D-49932DE0938D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB77879-006B-4908-BD0D-330960C923DF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
